--- a/Input_Files/Link_Budget_Calculator.xlsx
+++ b/Input_Files/Link_Budget_Calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanis\Desktop\CAPSTONE\STK_Simulation_Code\Input_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CC39AF-9D08-47F8-B3C4-B51B34A647E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA7DD56-BBA0-4E45-8596-9D768373C0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9600" yWindow="0" windowWidth="11688" windowHeight="12240" tabRatio="315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
